--- a/bom.xlsx
+++ b/bom.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Federico\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Federico\Desktop\k\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{BF8B5F06-9566-4A46-9853-ADEC6A627162}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A828E940-5486-432A-A9DF-2406959CE129}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{EF426629-EB5F-4B4B-B146-6BA97A67EE6F}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="21">
   <si>
     <t>PCB (see the production folder),1,See production folder for gerbers/fab files</t>
   </si>
@@ -80,13 +80,16 @@
   </si>
   <si>
     <t>3D Printed</t>
+  </si>
+  <si>
+    <t>AKKO Black &amp; Gold ISO Nordic Keycap Set (76-Key)</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="18" x14ac:knownFonts="1">
+  <fonts count="19" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -217,6 +220,14 @@
     <font>
       <sz val="11"/>
       <color theme="0"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -563,8 +574,9 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="42">
     <cellStyle name="20% - Colore 1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -1003,8 +1015,8 @@
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>14</v>
+      <c r="A8" s="1" t="s">
+        <v>20</v>
       </c>
       <c r="B8">
         <v>1</v>
